--- a/data/trans_orig/P39B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P39B-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2012</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2012 (tasa de respuesta: 97,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34477</t>
+          <t>32532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62002</t>
+          <t>60273</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31567</t>
+          <t>29911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51771</t>
+          <t>51799</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84814</t>
+          <t>84494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79924</t>
+          <t>79567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115109</t>
+          <t>114475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57533</t>
+          <t>56685</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87098</t>
+          <t>88205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145749</t>
+          <t>144431</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192784</t>
+          <t>191503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98173</t>
+          <t>99031</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135141</t>
+          <t>133644</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>87175</t>
+          <t>88770</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119565</t>
+          <t>122957</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>193693</t>
+          <t>195375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>244681</t>
+          <t>246745</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34534</t>
+          <t>35054</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63493</t>
+          <t>62728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20990</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>44627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61611</t>
+          <t>62331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99388</t>
+          <t>99778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>54774</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84943</t>
+          <t>85235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40901</t>
+          <t>39923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69149</t>
+          <t>70125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100885</t>
+          <t>101652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141761</t>
+          <t>142416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32766</t>
+          <t>32390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29489</t>
+          <t>27753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29984</t>
+          <t>28194</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54911</t>
+          <t>52567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69074</t>
+          <t>68358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101824</t>
+          <t>103150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65223</t>
+          <t>65299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95643</t>
+          <t>96367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140612</t>
+          <t>140508</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188220</t>
+          <t>187034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116117</t>
+          <t>117717</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157199</t>
+          <t>157383</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78721</t>
+          <t>77532</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>111853</t>
+          <t>110786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>204462</t>
+          <t>205675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>257077</t>
+          <t>256915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37464</t>
+          <t>38453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66790</t>
+          <t>69035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23385</t>
+          <t>23558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48374</t>
+          <t>48044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68528</t>
+          <t>68929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105567</t>
+          <t>105548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>56916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89027</t>
+          <t>89410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59696</t>
+          <t>60884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92961</t>
+          <t>93406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126659</t>
+          <t>126704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172261</t>
+          <t>173690</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31008</t>
+          <t>30046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55647</t>
+          <t>56726</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41775</t>
+          <t>41327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70973</t>
+          <t>68334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84512</t>
+          <t>86781</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121183</t>
+          <t>121864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41604</t>
+          <t>39993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67749</t>
+          <t>66788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,47 +2259,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>17,13%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>155577</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>132678</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>179106</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>17,82%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>29,02%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>155577</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>134865</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>178752</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>18,12%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>141206</t>
+          <t>139884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183452</t>
+          <t>183761</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52772</t>
+          <t>51070</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80058</t>
+          <t>78744</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>201171</t>
+          <t>200280</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>254736</t>
+          <t>252307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54774</t>
+          <t>54820</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90645</t>
+          <t>88577</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28123</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49935</t>
+          <t>50023</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89030</t>
+          <t>87874</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132275</t>
+          <t>129482</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116196</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156832</t>
+          <t>157554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52236</t>
+          <t>51295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>79756</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>175808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>227887</t>
+          <t>227942</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70913</t>
+          <t>70378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106633</t>
+          <t>105770</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36824</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65665</t>
+          <t>63729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113637</t>
+          <t>114398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161033</t>
+          <t>157968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>197640</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256213</t>
+          <t>253983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>99004</t>
+          <t>100383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143200</t>
+          <t>140486</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>315021</t>
+          <t>315639</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>383803</t>
+          <t>382315</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>274559</t>
+          <t>276211</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>334857</t>
+          <t>335018</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171058</t>
+          <t>169438</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>217423</t>
+          <t>216210</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>458635</t>
+          <t>461802</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>536134</t>
+          <t>536598</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88914</t>
+          <t>87839</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129837</t>
+          <t>131777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,82 +3132,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>13,94%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>82363</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>67009</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>101255</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>190451</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>166603</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>218449</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>13,74%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>82363</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>65778</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>100793</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>15,62%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>190451</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>162250</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>218618</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>190603</t>
+          <t>194103</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>245311</t>
+          <t>247436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175240</t>
+          <t>176781</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>223163</t>
+          <t>224107</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>376456</t>
+          <t>383175</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>454850</t>
+          <t>459378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29854</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54920</t>
+          <t>53817</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>37951</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65825</t>
+          <t>67847</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71761</t>
+          <t>72743</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>110228</t>
+          <t>110963</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>82797</t>
+          <t>84619</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>118449</t>
+          <t>119265</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>110021</t>
+          <t>106778</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>152812</t>
+          <t>148923</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>204951</t>
+          <t>204441</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>260153</t>
+          <t>258594</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>95585</t>
+          <t>96060</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>131951</t>
+          <t>132202</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>150793</t>
+          <t>152336</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>196150</t>
+          <t>199855</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>259474</t>
+          <t>259197</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>317530</t>
+          <t>319269</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>39888</t>
+          <t>40577</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>66674</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>88797</t>
+          <t>87997</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>125787</t>
+          <t>126395</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>135360</t>
+          <t>137172</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>182188</t>
+          <t>183268</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>70681</t>
+          <t>71347</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>105654</t>
+          <t>105178</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>171851</t>
+          <t>173081</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>220310</t>
+          <t>221176</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>256511</t>
+          <t>255777</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>316651</t>
+          <t>312931</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>31431</t>
+          <t>30289</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>35261</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>64316</t>
+          <t>62775</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>54206</t>
+          <t>54805</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>86498</t>
+          <t>87160</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>24272</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>43625</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>118107</t>
+          <t>117753</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>163480</t>
+          <t>162864</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>150576</t>
+          <t>148730</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>197365</t>
+          <t>198087</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21039</t>
+          <t>21572</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>40352</t>
+          <t>39409</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>260596</t>
+          <t>258525</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>317024</t>
+          <t>316728</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>288536</t>
+          <t>287232</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>347954</t>
+          <t>347410</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>121236</t>
+          <t>123711</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>165953</t>
+          <t>169369</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>131258</t>
+          <t>132058</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>179145</t>
+          <t>179896</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>23743</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>264608</t>
+          <t>266250</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>323952</t>
+          <t>326933</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>280858</t>
+          <t>283876</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>342171</t>
+          <t>342753</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>229505</t>
+          <t>225344</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>289387</t>
+          <t>290652</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>171045</t>
+          <t>171200</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>226785</t>
+          <t>228568</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>417218</t>
+          <t>415769</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>503766</t>
+          <t>499784</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>596398</t>
+          <t>596302</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>686360</t>
+          <t>687685</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>547198</t>
+          <t>551305</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>637148</t>
+          <t>639954</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1170765</t>
+          <t>1175536</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1301724</t>
+          <t>1303735</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>811620</t>
+          <t>814150</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>909397</t>
+          <t>910955</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>868580</t>
+          <t>865420</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>971601</t>
+          <t>973396</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1700314</t>
+          <t>1710577</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1854356</t>
+          <t>1848548</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>305660</t>
+          <t>305865</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>376353</t>
+          <t>380818</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>397935</t>
+          <t>399173</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>474808</t>
+          <t>474417</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>717410</t>
+          <t>724460</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>828074</t>
+          <t>826833</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>555392</t>
+          <t>551056</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>645343</t>
+          <t>641733</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>832057</t>
+          <t>832189</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>939276</t>
+          <t>932176</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1421712</t>
+          <t>1416938</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1555868</t>
+          <t>1545391</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2016 (tasa de respuesta: 96,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>29704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53659</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34113</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48924</t>
+          <t>48833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81495</t>
+          <t>83546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79724</t>
+          <t>79245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113984</t>
+          <t>114469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75845</t>
+          <t>77580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107365</t>
+          <t>109642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164295</t>
+          <t>165062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208458</t>
+          <t>210225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94264</t>
+          <t>94371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131036</t>
+          <t>130128</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82030</t>
+          <t>80658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>115041</t>
+          <t>115114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>187026</t>
+          <t>186102</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>234901</t>
+          <t>237444</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30760</t>
+          <t>30254</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56153</t>
+          <t>55154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35914</t>
+          <t>35516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63766</t>
+          <t>61775</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72417</t>
+          <t>72384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108729</t>
+          <t>109536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46998</t>
+          <t>46682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75884</t>
+          <t>76453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36476</t>
+          <t>36639</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60720</t>
+          <t>62016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90838</t>
+          <t>90034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129264</t>
+          <t>130507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46213</t>
+          <t>45466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>20601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42054</t>
+          <t>41712</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46850</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79152</t>
+          <t>77018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68947</t>
+          <t>67892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100925</t>
+          <t>101138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67888</t>
+          <t>66987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98164</t>
+          <t>98906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145015</t>
+          <t>145615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189221</t>
+          <t>191234</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76486</t>
+          <t>76953</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>108333</t>
+          <t>109767</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87894</t>
+          <t>87178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123616</t>
+          <t>120462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>172189</t>
+          <t>171711</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>221960</t>
+          <t>220997</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61036</t>
+          <t>62355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27677</t>
+          <t>26839</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49616</t>
+          <t>50853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66446</t>
+          <t>65702</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103411</t>
+          <t>101139</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42646</t>
+          <t>43055</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71524</t>
+          <t>72345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48124</t>
+          <t>47903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77916</t>
+          <t>77411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99307</t>
+          <t>99153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141570</t>
+          <t>141839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50936</t>
+          <t>52131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>35980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61148</t>
+          <t>62595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92332</t>
+          <t>91535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127868</t>
+          <t>127690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>22383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>43607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122038</t>
+          <t>120806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163169</t>
+          <t>160852</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119363</t>
+          <t>119273</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159343</t>
+          <t>158082</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31964</t>
+          <t>32430</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>55631</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>160653</t>
+          <t>155580</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>207593</t>
+          <t>201684</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53548</t>
+          <t>52831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85056</t>
+          <t>83672</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69129</t>
+          <t>68196</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104017</t>
+          <t>103889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61853</t>
+          <t>62460</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94723</t>
+          <t>95092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>30610</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52820</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99368</t>
+          <t>100085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>139429</t>
+          <t>139613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89595</t>
+          <t>89272</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129450</t>
+          <t>129368</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52690</t>
+          <t>53389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84677</t>
+          <t>84575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149658</t>
+          <t>150389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>200811</t>
+          <t>201834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>223461</t>
+          <t>225459</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>280729</t>
+          <t>282372</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>168369</t>
+          <t>168000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>213964</t>
+          <t>215501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>407355</t>
+          <t>407842</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>479889</t>
+          <t>480614</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>240475</t>
+          <t>238764</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>296938</t>
+          <t>293201</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>176094</t>
+          <t>176287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>222853</t>
+          <t>220864</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>428010</t>
+          <t>427501</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>500300</t>
+          <t>499751</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>112858</t>
+          <t>112174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>155454</t>
+          <t>155292</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73255</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108164</t>
+          <t>108167</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>194750</t>
+          <t>195387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>249672</t>
+          <t>250090</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146369</t>
+          <t>142122</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>192980</t>
+          <t>191407</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>117941</t>
+          <t>121546</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161490</t>
+          <t>163565</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>276119</t>
+          <t>274640</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>343101</t>
+          <t>340855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50403</t>
+          <t>50481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80691</t>
+          <t>80161</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44102</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74508</t>
+          <t>73071</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>104887</t>
+          <t>102193</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>145035</t>
+          <t>145445</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100970</t>
+          <t>100385</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139550</t>
+          <t>140856</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>121134</t>
+          <t>123695</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>165341</t>
+          <t>164495</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234947</t>
+          <t>234954</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>295117</t>
+          <t>292043</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>133777</t>
+          <t>133978</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>175596</t>
+          <t>176315</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>185547</t>
+          <t>183593</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>233290</t>
+          <t>230924</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>330351</t>
+          <t>332063</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>394268</t>
+          <t>393067</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>46881</t>
+          <t>48684</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>76052</t>
+          <t>78278</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71823</t>
+          <t>70595</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>106491</t>
+          <t>106031</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>128379</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>174732</t>
+          <t>173656</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>69689</t>
+          <t>70306</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>103206</t>
+          <t>101513</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>113081</t>
+          <t>114229</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>154084</t>
+          <t>157127</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>191956</t>
+          <t>192761</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>246082</t>
+          <t>244486</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>33013</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35576</t>
+          <t>35661</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>62189</t>
+          <t>62324</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>55572</t>
+          <t>56008</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>87337</t>
+          <t>88900</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>50304</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>73778</t>
+          <t>72799</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>219072</t>
+          <t>222031</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>277425</t>
+          <t>280175</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>276982</t>
+          <t>277508</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>339470</t>
+          <t>339454</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>41859</t>
+          <t>41519</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>248423</t>
+          <t>249919</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>305585</t>
+          <t>307038</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>277015</t>
+          <t>278920</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>337722</t>
+          <t>336322</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>139024</t>
+          <t>136192</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>188568</t>
+          <t>186791</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>147403</t>
+          <t>148187</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>200939</t>
+          <t>197883</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>25115</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>160540</t>
+          <t>158350</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>210103</t>
+          <t>210586</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>171400</t>
+          <t>173174</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>227458</t>
+          <t>228186</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>277054</t>
+          <t>275868</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>344460</t>
+          <t>343502</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>201891</t>
+          <t>203188</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>260678</t>
+          <t>261869</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>498143</t>
+          <t>500809</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>588924</t>
+          <t>591270</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>676041</t>
+          <t>671294</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>764456</t>
+          <t>769861</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>743449</t>
+          <t>736204</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>841358</t>
+          <t>836773</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1443979</t>
+          <t>1441900</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1576026</t>
+          <t>1577503</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>750712</t>
+          <t>744454</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>846239</t>
+          <t>844610</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>877077</t>
+          <t>878506</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>984509</t>
+          <t>980540</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1648775</t>
+          <t>1649079</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1797958</t>
+          <t>1790129</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>325158</t>
+          <t>323880</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>397682</t>
+          <t>399102</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>404016</t>
+          <t>403836</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>485090</t>
+          <t>483757</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>754003</t>
+          <t>750914</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>859499</t>
+          <t>859804</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>426289</t>
+          <t>424982</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>504930</t>
+          <t>502139</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>563060</t>
+          <t>567276</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>655585</t>
+          <t>655398</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1014664</t>
+          <t>1010376</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1136178</t>
+          <t>1127894</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2023 (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40803</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32734</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59488</t>
+          <t>60042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91013</t>
+          <t>89610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125861</t>
+          <t>126070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80394</t>
+          <t>82377</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109864</t>
+          <t>110396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>181503</t>
+          <t>181339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228077</t>
+          <t>227967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126727</t>
+          <t>127994</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>167303</t>
+          <t>167606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98448</t>
+          <t>98027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>128778</t>
+          <t>127921</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>235385</t>
+          <t>234106</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>285556</t>
+          <t>283448</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56011</t>
+          <t>54433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>84260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>61187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87906</t>
+          <t>87535</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124749</t>
+          <t>123514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162976</t>
+          <t>164782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66921</t>
+          <t>66630</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98308</t>
+          <t>97904</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84385</t>
+          <t>84170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117359</t>
+          <t>116384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161388</t>
+          <t>159956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206201</t>
+          <t>202179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34821</t>
+          <t>34626</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>30382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33163</t>
+          <t>32906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>59210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82015</t>
+          <t>81287</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118408</t>
+          <t>115850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70711</t>
+          <t>70146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97372</t>
+          <t>98041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158961</t>
+          <t>159327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203423</t>
+          <t>203779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90240</t>
+          <t>90370</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128683</t>
+          <t>126289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94996</t>
+          <t>92290</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123808</t>
+          <t>122357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>194405</t>
+          <t>193293</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240554</t>
+          <t>239455</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60141</t>
+          <t>60686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93298</t>
+          <t>92473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46759</t>
+          <t>47266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70025</t>
+          <t>70755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114302</t>
+          <t>114327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154020</t>
+          <t>152039</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66159</t>
+          <t>66804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97977</t>
+          <t>97971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>52832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75959</t>
+          <t>74647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127715</t>
+          <t>126212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166770</t>
+          <t>165876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38866</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>29456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51702</t>
+          <t>50963</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93939</t>
+          <t>92535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127686</t>
+          <t>128990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27365</t>
+          <t>27276</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43810</t>
+          <t>43914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125058</t>
+          <t>126343</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>162704</t>
+          <t>164278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83580</t>
+          <t>83428</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115368</t>
+          <t>115270</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50883</t>
+          <t>50937</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122259</t>
+          <t>122902</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158427</t>
+          <t>160955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54219</t>
+          <t>55893</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83258</t>
+          <t>84117</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31755</t>
+          <t>33622</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79151</t>
+          <t>78551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110425</t>
+          <t>109984</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51345</t>
+          <t>50717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79591</t>
+          <t>78616</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>30263</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48306</t>
+          <t>48423</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86490</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121361</t>
+          <t>120524</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>51275</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85571</t>
+          <t>85389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>26951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82892</t>
+          <t>82921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87741</t>
+          <t>85168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153827</t>
+          <t>152900</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182712</t>
+          <t>179558</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>235523</t>
+          <t>234994</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72826</t>
+          <t>84894</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>223438</t>
+          <t>223918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248496</t>
+          <t>232637</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437438</t>
+          <t>435801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>227835</t>
+          <t>228347</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282914</t>
+          <t>282996</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>274009</t>
+          <t>277720</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>676047</t>
+          <t>656662</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>520726</t>
+          <t>521252</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1001085</t>
+          <t>1046267</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132276</t>
+          <t>134713</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178843</t>
+          <t>179843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44789</t>
+          <t>46422</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>136841</t>
+          <t>134347</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173483</t>
+          <t>176612</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>301471</t>
+          <t>301627</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>139981</t>
+          <t>141363</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186560</t>
+          <t>186300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13276,17 +13276,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>140375</t>
+          <t>140374</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67484</t>
+          <t>69869</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>190940</t>
+          <t>191225</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>205846</t>
+          <t>205683</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>355095</t>
+          <t>356710</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30893</t>
+          <t>30387</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57443</t>
+          <t>56587</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36589</t>
+          <t>36232</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62320</t>
+          <t>60247</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>72679</t>
+          <t>73020</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>106157</t>
+          <t>109374</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>79239</t>
+          <t>78991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>115282</t>
+          <t>116886</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>114733</t>
+          <t>115441</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>156319</t>
+          <t>156487</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>202627</t>
+          <t>204352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>257928</t>
+          <t>262149</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99850</t>
+          <t>99285</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>138880</t>
+          <t>140672</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>191822</t>
+          <t>193263</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>301673</t>
+          <t>288703</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>308344</t>
+          <t>305505</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>429586</t>
+          <t>417336</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>68608</t>
+          <t>70289</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>97027</t>
+          <t>97670</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>132895</t>
+          <t>131949</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>145850</t>
+          <t>147221</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>195360</t>
+          <t>193037</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55775</t>
+          <t>55791</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>84111</t>
+          <t>85004</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>142923</t>
+          <t>141787</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>192233</t>
+          <t>192903</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>210595</t>
+          <t>213589</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>267225</t>
+          <t>269491</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>40561</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35007</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>60772</t>
+          <t>61222</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>53592</t>
+          <t>51913</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>91737</t>
+          <t>91174</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18922</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>49092</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>141497</t>
+          <t>141510</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>181222</t>
+          <t>184193</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>169984</t>
+          <t>168114</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>220961</t>
+          <t>224360</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>17311</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>48230</t>
+          <t>47460</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>158002</t>
+          <t>157030</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>196404</t>
+          <t>195448</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>185487</t>
+          <t>181988</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>232549</t>
+          <t>233669</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>90043</t>
+          <t>89175</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>121872</t>
+          <t>118843</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>93163</t>
+          <t>92887</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>127782</t>
+          <t>129106</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>113951</t>
+          <t>114289</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>147716</t>
+          <t>148188</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>116113</t>
+          <t>115036</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>154516</t>
+          <t>154505</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>175038</t>
+          <t>178727</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>239363</t>
+          <t>240026</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>163249</t>
+          <t>162704</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>238262</t>
+          <t>236162</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>352580</t>
+          <t>361013</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>456431</t>
+          <t>456943</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>599887</t>
+          <t>607246</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>693061</t>
+          <t>705529</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>546311</t>
+          <t>526184</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>746557</t>
+          <t>750979</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1168894</t>
+          <t>1161901</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1418069</t>
+          <t>1411888</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>709446</t>
+          <t>710633</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>806655</t>
+          <t>803636</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>917566</t>
+          <t>915366</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1507472</t>
+          <t>1552096</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1675936</t>
+          <t>1672059</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2316213</t>
+          <t>2324872</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>389414</t>
+          <t>390554</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>470655</t>
+          <t>471450</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>380038</t>
+          <t>370007</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>521771</t>
+          <t>522476</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>798225</t>
+          <t>789660</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>966814</t>
+          <t>963517</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>427029</t>
+          <t>427034</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>507762</t>
+          <t>500174</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>520896</t>
+          <t>502593</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>703440</t>
+          <t>706159</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>972639</t>
+          <t>961262</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1173183</t>
+          <t>1176689</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
